--- a/docs/downloads/20260903_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260903_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,10 @@
     <col width="9" customWidth="1" min="25" max="25"/>
     <col width="9" customWidth="1" min="26" max="26"/>
     <col width="9" customWidth="1" min="27" max="27"/>
-    <col width="42" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="42" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,8 +558,11 @@
       <c r="V3" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Y3" s="3" t="n">
         <v>46262</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -683,22 +689,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="Y4" s="6" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="Z4" s="6" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AA4" s="6" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="AB4" s="5" t="inlineStr">
+      <c r="AB4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AC4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AD4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -794,18 +815,29 @@
         <f>W5/$D$5</f>
         <v/>
       </c>
-      <c r="Y5" s="12">
+      <c r="Y5" s="10">
         <f>Z5-W5</f>
         <v/>
       </c>
-      <c r="Z5" s="12" t="n">
+      <c r="Z5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AA5" s="11">
         <f>Z5/$D$5</f>
         <v/>
       </c>
-      <c r="AB5" s="8" t="inlineStr">
+      <c r="AB5" s="12">
+        <f>AC5-Z5</f>
+        <v/>
+      </c>
+      <c r="AC5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD5" s="13">
+        <f>AC5/$D$5</f>
+        <v/>
+      </c>
+      <c r="AE5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -901,18 +933,29 @@
         <f>W6/$D$6</f>
         <v/>
       </c>
-      <c r="Y6" s="12">
+      <c r="Y6" s="10">
         <f>Z6-W6</f>
         <v/>
       </c>
-      <c r="Z6" s="12" t="n">
+      <c r="Z6" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AA6" s="11">
         <f>Z6/$D$6</f>
         <v/>
       </c>
-      <c r="AB6" s="8" t="inlineStr">
+      <c r="AB6" s="12">
+        <f>AC6-Z6</f>
+        <v/>
+      </c>
+      <c r="AC6" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD6" s="13">
+        <f>AC6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AE6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -1008,18 +1051,29 @@
         <f>W7/$D$7</f>
         <v/>
       </c>
-      <c r="Y7" s="12">
+      <c r="Y7" s="10">
         <f>Z7-W7</f>
         <v/>
       </c>
-      <c r="Z7" s="12" t="n">
+      <c r="Z7" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AA7" s="11">
         <f>Z7/$D$7</f>
         <v/>
       </c>
-      <c r="AB7" s="8" t="inlineStr">
+      <c r="AB7" s="12">
+        <f>AC7-Z7</f>
+        <v/>
+      </c>
+      <c r="AC7" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD7" s="13">
+        <f>AC7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AE7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -1115,18 +1169,29 @@
         <f>W8/$D$8</f>
         <v/>
       </c>
-      <c r="Y8" s="12">
+      <c r="Y8" s="10">
         <f>Z8-W8</f>
         <v/>
       </c>
-      <c r="Z8" s="12" t="n">
+      <c r="Z8" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AA8" s="11">
         <f>Z8/$D$8</f>
         <v/>
       </c>
-      <c r="AB8" s="8" t="inlineStr">
+      <c r="AB8" s="12">
+        <f>AC8-Z8</f>
+        <v/>
+      </c>
+      <c r="AC8" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD8" s="13">
+        <f>AC8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AE8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1222,18 +1287,29 @@
         <f>W9/$D$9</f>
         <v/>
       </c>
-      <c r="Y9" s="12">
+      <c r="Y9" s="10">
         <f>Z9-W9</f>
         <v/>
       </c>
-      <c r="Z9" s="12" t="n">
+      <c r="Z9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AA9" s="11">
         <f>Z9/$D$9</f>
         <v/>
       </c>
-      <c r="AB9" s="8" t="inlineStr">
+      <c r="AB9" s="12">
+        <f>AC9-Z9</f>
+        <v/>
+      </c>
+      <c r="AC9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="13">
+        <f>AC9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AE9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1319,18 +1395,29 @@
         <f>W10/$D$10</f>
         <v/>
       </c>
-      <c r="Y10" s="12">
+      <c r="Y10" s="10">
         <f>Z10-W10</f>
         <v/>
       </c>
-      <c r="Z10" s="12" t="n">
+      <c r="Z10" s="10" t="n">
         <v>349</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AA10" s="11">
         <f>Z10/$D$10</f>
         <v/>
       </c>
-      <c r="AB10" s="8" t="inlineStr">
+      <c r="AB10" s="12">
+        <f>AC10-Z10</f>
+        <v/>
+      </c>
+      <c r="AC10" s="12" t="n">
+        <v>353</v>
+      </c>
+      <c r="AD10" s="13">
+        <f>AC10/$D$10</f>
+        <v/>
+      </c>
+      <c r="AE10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
@@ -1384,23 +1471,35 @@
         <f>W11/$D$11</f>
         <v/>
       </c>
-      <c r="Y11" s="12">
+      <c r="Y11" s="10">
         <f>Z11-W11</f>
         <v/>
       </c>
-      <c r="Z11" s="12" t="n">
+      <c r="Z11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AA11" s="11">
         <f>Z11/$D$11</f>
         <v/>
       </c>
-      <c r="AB11" s="8" t="inlineStr"/>
+      <c r="AB11" s="12">
+        <f>AC11-Z11</f>
+        <v/>
+      </c>
+      <c r="AC11" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="13">
+        <f>AC11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AE11" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="Y3:AA3"/>
     <mergeCell ref="M3:O3"/>
+    <mergeCell ref="AB3:AD3"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="V3:X3"/>
